--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_7_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_7_R1.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5843</v>
+        <v>3.5513</v>
       </c>
       <c r="E2" t="n">
-        <v>1.759</v>
+        <v>1.9949</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8253</v>
+        <v>1.5564</v>
       </c>
       <c r="G2" t="n">
         <v>1.6379</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1784</v>
+        <v>0.1454</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7758</v>
+        <v>0.507</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0289</v>
+        <v>2.9232</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6227</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4062</v>
+        <v>2.0386</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3937</v>
+        <v>1.3421</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0347</v>
+        <v>-0.3409</v>
       </c>
       <c r="I3" t="n">
-        <v>2.359</v>
+        <v>1.683</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4151</v>
+        <v>0.6744</v>
       </c>
       <c r="K3" t="n">
-        <v>2.679</v>
+        <v>0.4068</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7361</v>
+        <v>0.2676</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9786</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6443</v>
+        <v>-0.7477</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6229</v>
+        <v>1.4154</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2204</v>
+        <v>-0.7205</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.4676</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5878</v>
+        <v>-0.2528</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3939</v>
+        <v>2.8005</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4561</v>
+        <v>1.4615</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9378</v>
+        <v>1.339</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3421</v>
+        <v>4.3937</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3409</v>
+        <v>2.0347</v>
       </c>
       <c r="I4" t="n">
-        <v>1.683</v>
+        <v>2.359</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6744</v>
+        <v>3.4151</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4068</v>
+        <v>2.679</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2676</v>
+        <v>0.7361</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.9786</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7477</v>
+        <v>-0.6443</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4154</v>
+        <v>1.6229</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2498</v>
+        <v>-1.4488</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8962</v>
+        <v>-0.7938</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3536</v>
+        <v>-0.655</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8254</v>
+        <v>1.9941</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0047</v>
+        <v>0.2406</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8207</v>
+        <v>1.7535</v>
       </c>
       <c r="G5" t="n">
         <v>1.9015</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6818</v>
+        <v>-0.5131</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0769</v>
       </c>
       <c r="V5" t="n">
         <v>0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7307</v>
+        <v>0.9837</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4447</v>
+        <v>0.7986</v>
       </c>
       <c r="F6" t="n">
-        <v>0.286</v>
+        <v>0.1852</v>
       </c>
       <c r="G6" t="n">
         <v>0.4916</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1489</v>
+        <v>0.402</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6717</v>
+        <v>0.5709</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1418</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.251</v>
+        <v>-0.0596</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1277</v>
+        <v>-0.8239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3787</v>
+        <v>0.7643</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4389</v>
+        <v>-1.3677</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0886</v>
+        <v>-0.0526</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6497</v>
+        <v>-1.3151</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4308</v>
+        <v>-1.6997</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6148</v>
+        <v>0.0336</v>
       </c>
       <c r="L7" t="n">
-        <v>0.184</v>
+        <v>-1.7334</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0081</v>
+        <v>0.3321</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4738</v>
+        <v>-0.0862</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4657</v>
+        <v>0.4183</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6502</v>
+        <v>-0.4599</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3031</v>
+        <v>-0.1964</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9533</v>
+        <v>-0.2636</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1016</v>
+        <v>-0.1131</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6627</v>
+        <v>-0.7607</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7643</v>
+        <v>0.6476</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3677</v>
+        <v>-0.4389</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0526</v>
+        <v>-2.0886</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3151</v>
+        <v>1.6497</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6997</v>
+        <v>-0.4308</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0336</v>
+        <v>-0.6148</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7334</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3321</v>
+        <v>-0.0081</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0862</v>
+        <v>-1.4738</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4183</v>
+        <v>1.4657</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2987</v>
+        <v>-1.0143</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0351</v>
+        <v>-0.3299</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2636</v>
+        <v>-0.6844</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0302</v>
+        <v>-0.3168</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3672</v>
+        <v>-0.7211</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3371</v>
+        <v>0.4043</v>
       </c>
       <c r="G9" t="n">
         <v>0.6618000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2179</v>
+        <v>-0.0688</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.195</v>
+        <v>-0.1278</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6778999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>B. TAYLOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1363</v>
+        <v>-1.1333</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7363</v>
+        <v>-1.0097</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>-0.1236</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0298</v>
+        <v>1.372</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4681</v>
+        <v>-0.7226</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4383</v>
+        <v>2.0946</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7503</v>
+        <v>1.5653</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1947</v>
+        <v>-0.1646</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5556</v>
+        <v>1.7298</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2795</v>
+        <v>-0.1933</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2734</v>
+        <v>-0.5581</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9939</v>
+        <v>0.3648</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3901</v>
+        <v>-0.1858</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1098</v>
+        <v>-0.2555</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2803</v>
+        <v>0.0696</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. TAYLOR</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4865</v>
+        <v>-1.2646</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1276</v>
+        <v>-1.3696</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3589</v>
+        <v>0.105</v>
       </c>
       <c r="G11" t="n">
-        <v>1.372</v>
+        <v>0.9585</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7226</v>
+        <v>-0.4969</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0946</v>
+        <v>1.4554</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5653</v>
+        <v>1.438</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1646</v>
+        <v>0.6085</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7298</v>
+        <v>0.8296</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1933</v>
+        <v>-0.4795</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5581</v>
+        <v>-1.1053</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3648</v>
+        <v>0.6258</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3195</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.539</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3734</v>
+        <v>-0.5423</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1656</v>
+        <v>-0.1114</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8035</v>
+        <v>-1.3812</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1989</v>
+        <v>-1.7796</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3954</v>
+        <v>0.3983</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0989</v>
+        <v>-1.0298</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.748</v>
+        <v>-1.4681</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6492</v>
+        <v>0.4383</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4417</v>
+        <v>-0.7503</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5153</v>
+        <v>-0.1947</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0736</v>
+        <v>-0.5556</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3428</v>
+        <v>-0.2795</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2327</v>
+        <v>-1.2734</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5756</v>
+        <v>0.9939</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2232</v>
+        <v>-0.635</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5975</v>
+        <v>-0.1531</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8206</v>
+        <v>-0.4819</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8537</v>
+        <v>-2.0051</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7234</v>
+        <v>-3.1989</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1303</v>
+        <v>1.1938</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9585</v>
+        <v>-1.0989</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4969</v>
+        <v>-1.748</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4554</v>
+        <v>0.6492</v>
       </c>
       <c r="J13" t="n">
-        <v>1.438</v>
+        <v>-1.4417</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6085</v>
+        <v>-1.5153</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8296</v>
+        <v>0.0736</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4795</v>
+        <v>0.3428</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1053</v>
+        <v>-0.2327</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6258</v>
+        <v>0.5756</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.7834</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2428</v>
+        <v>0.0215</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8962</v>
+        <v>-0.5975</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3466</v>
+        <v>0.619</v>
       </c>
       <c r="V13" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.605600000000001</v>
+        <v>5.979099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6566</v>
+        <v>-4.283300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10.2623</v>
+        <v>10.2624</v>
       </c>
       <c r="G14" t="n">
         <v>8.8238</v>
@@ -1519,7 +1519,7 @@
         <v>13.9194</v>
       </c>
       <c r="J14" t="n">
-        <v>7.096499999999999</v>
+        <v>7.0965</v>
       </c>
       <c r="K14" t="n">
         <v>3.3833</v>
@@ -1537,7 +1537,7 @@
         <v>10.2063</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000199999999999978</v>
+        <v>0.0001999999999990898</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5978</v>
@@ -1546,13 +1546,13 @@
         <v>11.598</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.5044</v>
+        <v>-5.131</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6172</v>
+        <v>-4.2436</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8874</v>
+        <v>-0.8873000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>2.2862</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0563</v>
+        <v>3.8375</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4745</v>
+        <v>4.3566</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4183</v>
+        <v>-0.5191</v>
       </c>
       <c r="G15" t="n">
         <v>2.0334</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3992</v>
+        <v>1.1804</v>
       </c>
       <c r="T15" t="n">
-        <v>0.586</v>
+        <v>0.4681</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8132</v>
+        <v>0.7123</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5087</v>
+        <v>2.1082</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8891</v>
+        <v>1.1748</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6196</v>
+        <v>0.9333</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9153</v>
+        <v>3.0699</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1427</v>
+        <v>1.3133</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2275</v>
+        <v>1.7566</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4015</v>
+        <v>3.0772</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3647</v>
+        <v>1.2639</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>1.8134</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4862</v>
+        <v>-0.0073</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.222</v>
+        <v>0.0495</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2643</v>
+        <v>-0.0568</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2713</v>
+        <v>1.2522</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4876</v>
+        <v>0.4171</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7837</v>
+        <v>0.8351</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>-1.7501</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9069</v>
+        <v>1.768</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1748</v>
+        <v>1.4173</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0817</v>
+        <v>0.3507</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3683</v>
+        <v>0.9153</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6326</v>
+        <v>1.1427</v>
       </c>
       <c r="I17" t="n">
+        <v>-0.2275</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.4015</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.3647</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.4862</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.222</v>
+      </c>
+      <c r="O17" t="n">
         <v>-0.2643</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.4068</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.1932</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.7863</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.9615</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.4395</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.5221</v>
-      </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7705</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1924</v>
+        <v>0.5149</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6871</v>
+        <v>1.671</v>
       </c>
       <c r="E18" t="n">
-        <v>0.821</v>
+        <v>-0.4107</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8661</v>
+        <v>2.0817</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0699</v>
+        <v>1.3683</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3133</v>
+        <v>1.6326</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7566</v>
+        <v>-0.2643</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0772</v>
+        <v>0.4068</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2639</v>
+        <v>1.1932</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8134</v>
+        <v>-0.7863</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0073</v>
+        <v>0.9615</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0495</v>
+        <v>0.4395</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0568</v>
+        <v>0.5221</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8312</v>
+        <v>0.5346</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0633</v>
+        <v>0.3422</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7679</v>
+        <v>0.1924</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5343</v>
+        <v>0.4993</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2719</v>
+        <v>-1.7437</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8061</v>
+        <v>2.243</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6655</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7358</v>
+        <v>0.7009</v>
       </c>
       <c r="T19" t="n">
-        <v>0.999</v>
+        <v>0.5272</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2631</v>
+        <v>0.1737</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1879</v>
+        <v>-0.0027</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4265</v>
+        <v>-0.3085</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2386</v>
+        <v>0.3058</v>
       </c>
       <c r="G20" t="n">
         <v>-0.614</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0378</v>
+        <v>0.1474</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2609</v>
+        <v>0.3282</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4486</v>
+        <v>-0.3979</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0407</v>
+        <v>0.0772</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4079</v>
+        <v>-0.4751</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5456</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0448</v>
+        <v>0.0059</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V21" t="n">
         <v>0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0808</v>
+        <v>-1.0973</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.548</v>
+        <v>-1.4301</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4672</v>
+        <v>0.3328</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5758</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3506</v>
+        <v>0.3341</v>
       </c>
       <c r="T22" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3427</v>
+        <v>0.2082</v>
       </c>
       <c r="V22" t="n">
         <v>1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1107</v>
+        <v>-2.6897</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5411</v>
+        <v>-2.1872</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5697</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-2.705</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.478</v>
+        <v>-0.0569</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2609</v>
+        <v>0.3282</v>
       </c>
       <c r="V23" t="n">
         <v>0.5361</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1565</v>
+        <v>-3.4905</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4298</v>
+        <v>-2.5582</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2734</v>
+        <v>-0.9323</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.7381</v>
+        <v>-2.1638</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0311</v>
+        <v>-0.3805</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.707</v>
+        <v>-1.7833</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.5656</v>
+        <v>0.0166</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.598</v>
+        <v>0.6925</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9676</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1725</v>
+        <v>-2.1804</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4331</v>
+        <v>-1.073</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.1074</v>
       </c>
       <c r="P24" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2801</v>
+        <v>-0.1669</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1537</v>
+        <v>-0.2552</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1264</v>
+        <v>0.0883</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5907</v>
+        <v>-3.78</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3223</v>
+        <v>-4.7482</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2684</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.1638</v>
+        <v>-4.203</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3805</v>
+        <v>1.3381</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7833</v>
+        <v>-5.5411</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0166</v>
+        <v>-3.8169</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6925</v>
+        <v>1.6139</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-5.4308</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1804</v>
+        <v>-0.3861</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.073</v>
+        <v>-0.2759</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1074</v>
+        <v>-0.1103</v>
       </c>
       <c r="P25" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q25" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2671</v>
+        <v>0.637</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0193</v>
+        <v>0.2284</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2478</v>
+        <v>0.4086</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.7237</v>
+        <v>-4.0315</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6918</v>
+        <v>-3.9017</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9681999999999999</v>
+        <v>-0.1299</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.203</v>
+        <v>-3.7381</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3381</v>
+        <v>-1.0311</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.5411</v>
+        <v>-2.707</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.8169</v>
+        <v>-2.5656</v>
       </c>
       <c r="K26" t="n">
-        <v>1.6139</v>
+        <v>-0.598</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.4308</v>
+        <v>-1.9676</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3861</v>
+        <v>-1.1725</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2759</v>
+        <v>-0.4331</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1103</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3066</v>
+        <v>0.405</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.3181</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4086</v>
+        <v>0.7231</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.9304</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="27">
@@ -2518,40 +2518,40 @@
         <v>-5.605599999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.2623</v>
+        <v>-10.2624</v>
       </c>
       <c r="F27" t="n">
-        <v>4.656599999999999</v>
+        <v>4.6566</v>
       </c>
       <c r="G27" t="n">
         <v>-8.823900000000002</v>
       </c>
       <c r="H27" t="n">
-        <v>5.0955</v>
+        <v>5.095499999999999</v>
       </c>
       <c r="I27" t="n">
         <v>-13.9194</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.727599999999999</v>
+        <v>-1.7276</v>
       </c>
       <c r="K27" t="n">
-        <v>8.4787</v>
+        <v>8.478699999999998</v>
       </c>
       <c r="L27" t="n">
         <v>-10.206</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.096200000000001</v>
+        <v>-7.0962</v>
       </c>
       <c r="N27" t="n">
         <v>-3.3833</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.713099999999999</v>
+        <v>-3.7131</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="Q27" t="n">
         <v>-11.5978</v>
@@ -2563,7 +2563,7 @@
         <v>5.5044</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8873999999999994</v>
+        <v>0.8873</v>
       </c>
       <c r="U27" t="n">
         <v>4.6171</v>
